--- a/input/Studies/MEET2/CompressorDeltaH.xlsx
+++ b/input/Studies/MEET2/CompressorDeltaH.xlsx
@@ -930,7 +930,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BA6"/>
+  <dimension ref="A1:BC6"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="39.5703125" defaultRowHeight="15"/>
   <cols>
     <col width="11.42578125" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -1249,6 +1249,16 @@
           <t>Factor Tag</t>
         </is>
       </c>
+      <c r="BB1" t="inlineStr">
+        <is>
+          <t>CCEE Ratio Distribution</t>
+        </is>
+      </c>
+      <c r="BC1" t="inlineStr">
+        <is>
+          <t>Crankcase Emissions Flag</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1434,6 +1444,12 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BB2" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="BC2" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -1619,6 +1635,12 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BB3" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="BC3" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -1804,6 +1826,12 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BB4" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="BC4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -1989,6 +2017,12 @@
           <t>ts_compressor</t>
         </is>
       </c>
+      <c r="BB5" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="BC5" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -2173,6 +2207,12 @@
         <is>
           <t>ts_compressor</t>
         </is>
+      </c>
+      <c r="BB6" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="BC6" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
